--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1324,7 +1324,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>EE: White Paper 2024-30 · SG: NAIS 2.0 2023 · DE: Aktionsplan 2023 · ES: Estrategia 2024 · PT: ANIA 2026-30</t>
+          <t>EE: White Paper 2024-30 · SG: Update NAIS may-2026 = estrategia vigente (decisión operador) · DE: Aktionsplan 2023 · ES: Estrategia 2024 · PT: ANIA 2026-30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Aplicantes e Inventores de patentes IA (83-84)</t>
+          <t>Aplicantes (83)=país del solicitante · Inventores (84)=país del inventor</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>NO existen en OECD.AI. Lens.org/Espacenet: CPC G06N facetado por país del SOLICITANTE / del INVENTOR.</t>
+          <t>NO existen en OECD.AI. Consultas listas en patentes_consultas_lens_espacenet.md (Lens facetado por país de la parte). Falta: lista CPC + ventana de ILIA 2025 (decisión: replicar).</t>
         </is>
       </c>
     </row>
@@ -3080,17 +3080,17 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Decisiones metodológicas</t>
+          <t>Decisiones metodológicas (estado)</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>UE / SG</t>
+          <t>UE/SG/EE</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>(a) cómo puntuar el EU AI Act como 'iniciativa legal' en países UE; (b) si el Update SG may-2026 cambia 'Antigüedad'; (c) confirmar ISO SC42 de Estonia (=0).</t>
+          <t>RESUELTO 2026-06-16: EU AI Act=iniciativa legal (128=3); SG Antigüedad (104)=4 (Update may-2026); ERNC=renovables total; patentes 83=solicitante/84=inventor. PENDIENTE: confirmar ISO SC42 Estonia (=0) en iso.org; lista CPC+ventana de patentes de ILIA 2025.</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1399,9 +1399,9 @@
           <t>Estrategia</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -1875,9 +1875,9 @@
           <t>Estrategia</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>1 (BAJA)</t>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>PT: solo principio en EDN, no eje en ANIA</t>
+          <t>EE: validado en Valge raamat (no es eje; 'kestlik areng' = econ. de datos); PT: solo principio en EDN, no eje en ANIA</t>
         </is>
       </c>
     </row>
@@ -1918,9 +1918,9 @@
           <t>Estrategia</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>2 (PRELIM)</t>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>PT: consulta pública con resultados</t>
+          <t>EE: stakeholders ('Kaasatud osapooled'), no consulta ciudadana; PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>
@@ -1961,16 +1961,16 @@
           <t>Estrategia</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>3 (PRELIM)</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
-        </is>
-      </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
           <t>4 (PRELIM)</t>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>PT: Gob+4</t>
+          <t>EE: Gob+3 (ITL/empresas + universidades + vabaühendused), p.8/12; PT: Gob+4</t>
         </is>
       </c>
     </row>
@@ -2004,9 +2004,9 @@
           <t>Estrategia</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>4 (PRELIM)</t>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1877,7 +1877,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>EE: validado en Valge raamat (no es eje; 'kestlik areng' = econ. de datos); PT: solo principio en EDN, no eje en ANIA</t>
+          <t>EE: validado con texto primario — IA verde/ODS/herramienta de sostenibilidad/rohejalajälg; PT: solo principio en EDN, no eje en ANIA</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1920,19 +1920,19 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>1 (PRELIM)</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
           <t>3 (PRELIM)</t>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>EE: stakeholders ('Kaasatud osapooled'), no consulta ciudadana; PT: consulta pública con resultados</t>
+          <t>EE: 2 encuestas ómnibus (2150 residentes) + 220 entrevistas, resultados publicados; PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1920,32 +1920,32 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>1 (PRELIM)</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>3 (PRELIM)</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>EE: 2 encuestas ómnibus (2150 residentes) + 220 entrevistas, resultados publicados; PT: consulta pública con resultados</t>
+          <t>EE: &gt;1 mecanismo (2 encuestas ómnibus 2150 residentes + 220 entrevistas), resultados publicados; PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>EE: Gob+3 (ITL/empresas + universidades + vabaühendused), p.8/12; PT: Gob+4</t>
+          <t>EE: Gob+4 (privado + academia + ONG vabaühendused + público general/encuestas 2150), p.8/12 + PA p.6; PT: Gob+4</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -2798,37 +2798,37 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>EMBER</t>
+          <t>EMBER 2025</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>80,90%</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>2024, renovables total. ES/PT/DE: ERNC excl. gran hidro es menor (ver energia_*.md)</t>
+          <t>Energía limpia = renovables + NUCLEAR (incl. hidro). EMBER 2025, determinístico (energia_limpia_ember2025.py). Solo ES tiene nuclear (18,79%). A confirmar con CENIA</t>
         </is>
       </c>
     </row>

--- a/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
+++ b/data/paises_extra/Planilla_ILIA2026_paises_extra.xlsx
@@ -1404,9 +1404,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -1424,7 +1424,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>SG: validado (NAIS se revisa 1.0→2.0→Update 2026; métricas de proyecto)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="n"/>
@@ -1880,16 +1884,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>1 (PRELIM)</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
-        </is>
-      </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1902,7 +1906,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>EE: validado con texto primario — IA verde/ODS/herramienta de sostenibilidad/rohejalajälg; PT: solo principio en EDN, no eje en ANIA</t>
+          <t>EE: validado (IA verde/ODS); SG: validado (resource-efficient/'green' AI, Green Data Centre Roadmap); PT: solo principio en EDN, no eje en ANIA</t>
         </is>
       </c>
     </row>
@@ -1923,9 +1927,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -1945,7 +1949,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>EE: &gt;1 mecanismo (2 encuestas ómnibus 2150 residentes + 220 entrevistas), resultados publicados; PT: consulta pública con resultados</t>
+          <t>EE: &gt;1 mecanismo (encuestas 2150 + 220 entrevistas); SG: sin mecanismo ciudadano (consulta solo a representantes del ecosistema → cuenta en 121); PT: consulta pública con resultados</t>
         </is>
       </c>
     </row>
@@ -1966,9 +1970,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>3 (PRELIM)</t>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>EE: Gob+4 (privado + academia + ONG vabaühendused + público general/encuestas 2150), p.8/12 + PA p.6; PT: Gob+4</t>
+          <t>EE: Gob+4 (privado+academia+ONG+público); SG: Gob+3 (industria+academia+non-profit; SCAI/RAISE.SG); PT: Gob+4</t>
         </is>
       </c>
     </row>
@@ -2009,27 +2013,31 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>4 (PRELIM)</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>4 (PRELIM)</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>4 (PRELIM)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>SG: validado — Whole-of-Nation + Tripartite (Gob/NTUC/empleadores) + AI Verify Foundation (non-profit)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="7" t="n"/>
@@ -2310,9 +2318,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>1 (PRELIM)</t>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -2330,7 +2338,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>SG: validado — enfoque 'risk-based, tiered' (NAIS 2.0 p.59; Update p.17)</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="7" t="n"/>
